--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N110_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N110_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>55.22559557170933</v>
+        <v>8.974159280402766</v>
       </c>
       <c r="D2" t="n">
-        <v>19.43971580458297</v>
+        <v>3.158953818244733</v>
       </c>
       <c r="E2" t="n">
-        <v>13.60696375879222</v>
+        <v>2.211131610803736</v>
       </c>
       <c r="F2" t="n">
-        <v>16.14131787762683</v>
+        <v>2.62296415511436</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>60.60289399452062</v>
+        <v>9.847970274109601</v>
       </c>
       <c r="D3" t="n">
-        <v>62.13574410590899</v>
+        <v>10.09705841721021</v>
       </c>
       <c r="E3" t="n">
-        <v>13.60696375879222</v>
+        <v>2.211131610803736</v>
       </c>
       <c r="F3" t="n">
-        <v>16.14131787762683</v>
+        <v>2.62296415511436</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>55.26118821252238</v>
+        <v>8.979943084534886</v>
       </c>
       <c r="D4" t="n">
-        <v>34.68788199261329</v>
+        <v>5.63678082379966</v>
       </c>
       <c r="E4" t="n">
-        <v>13.60696375879222</v>
+        <v>2.211131610803736</v>
       </c>
       <c r="F4" t="n">
-        <v>16.14131787762683</v>
+        <v>2.62296415511436</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>48.0342921610613</v>
+        <v>7.805572476172462</v>
       </c>
       <c r="D5" t="n">
-        <v>49.55644984495994</v>
+        <v>8.052923099805989</v>
       </c>
       <c r="E5" t="n">
-        <v>13.60696375879222</v>
+        <v>2.211131610803736</v>
       </c>
       <c r="F5" t="n">
-        <v>16.14131787762683</v>
+        <v>2.62296415511436</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>47.97488730738855</v>
+        <v>7.795919187450639</v>
       </c>
       <c r="D6" t="n">
-        <v>49.38257837919208</v>
+        <v>8.024668986618714</v>
       </c>
       <c r="E6" t="n">
-        <v>13.60696375879222</v>
+        <v>2.211131610803736</v>
       </c>
       <c r="F6" t="n">
-        <v>16.14131787762683</v>
+        <v>2.62296415511436</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>23.50531854708632</v>
+        <v>3.819614263901527</v>
       </c>
       <c r="D7" t="n">
-        <v>16.31474755104476</v>
+        <v>2.651146477044774</v>
       </c>
       <c r="E7" t="n">
-        <v>13.60696375879222</v>
+        <v>2.211131610803736</v>
       </c>
       <c r="F7" t="n">
-        <v>16.14131787762683</v>
+        <v>2.62296415511436</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>22.99244990323743</v>
+        <v>3.736273109276083</v>
       </c>
       <c r="D8" t="n">
-        <v>30.17093240484034</v>
+        <v>4.902776515786555</v>
       </c>
       <c r="E8" t="n">
-        <v>13.60696375879222</v>
+        <v>2.211131610803736</v>
       </c>
       <c r="F8" t="n">
-        <v>16.14131787762683</v>
+        <v>2.62296415511436</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>38.93711898573648</v>
+        <v>6.327281835182178</v>
       </c>
       <c r="D9" t="n">
-        <v>16.39453864694361</v>
+        <v>2.664112530128337</v>
       </c>
       <c r="E9" t="n">
-        <v>13.60696375879222</v>
+        <v>2.211131610803736</v>
       </c>
       <c r="F9" t="n">
-        <v>16.14131787762683</v>
+        <v>2.62296415511436</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>34.82997082421216</v>
+        <v>5.659870258934476</v>
       </c>
       <c r="D10" t="n">
-        <v>23.66976616951574</v>
+        <v>3.846337002546308</v>
       </c>
       <c r="E10" t="n">
-        <v>13.60696375879222</v>
+        <v>2.211131610803736</v>
       </c>
       <c r="F10" t="n">
-        <v>16.14131787762683</v>
+        <v>2.62296415511436</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>55.06512795476442</v>
+        <v>8.948083292649219</v>
       </c>
       <c r="D11" t="n">
-        <v>48.03164639079171</v>
+        <v>7.805142538503652</v>
       </c>
       <c r="E11" t="n">
-        <v>13.60696375879222</v>
+        <v>2.211131610803736</v>
       </c>
       <c r="F11" t="n">
-        <v>16.14131787762683</v>
+        <v>2.62296415511436</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>54.61083058527324</v>
+        <v>8.874259970106902</v>
       </c>
       <c r="D12" t="n">
-        <v>47.77037339058904</v>
+        <v>7.76268567597072</v>
       </c>
       <c r="E12" t="n">
-        <v>13.60696375879222</v>
+        <v>2.211131610803736</v>
       </c>
       <c r="F12" t="n">
-        <v>16.14131787762683</v>
+        <v>2.62296415511436</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>67.84319442970957</v>
+        <v>11.02451909482781</v>
       </c>
       <c r="D13" t="n">
-        <v>60.93752327601779</v>
+        <v>9.902347532352891</v>
       </c>
       <c r="E13" t="n">
-        <v>13.60696375879222</v>
+        <v>2.211131610803736</v>
       </c>
       <c r="F13" t="n">
-        <v>16.14131787762683</v>
+        <v>2.62296415511436</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
